--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/46.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/46.xlsx
@@ -426,13 +426,13 @@
         <v>0.7388780076351955</v>
       </c>
       <c r="E2">
-        <v>-9.747886542242629</v>
+        <v>-18.30359135509633</v>
       </c>
       <c r="F2">
-        <v>-7.467842360222639</v>
+        <v>-8.261188356694143</v>
       </c>
       <c r="G2">
-        <v>-7.451386982096539</v>
+        <v>-12.57781309729552</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>1.055512172703375</v>
       </c>
       <c r="E3">
-        <v>-9.584204849235384</v>
+        <v>-18.08737483512611</v>
       </c>
       <c r="F3">
-        <v>-7.798937461875115</v>
+        <v>-8.329959202366187</v>
       </c>
       <c r="G3">
-        <v>-7.143916754591189</v>
+        <v>-11.65234016015564</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>1.25009799426809</v>
       </c>
       <c r="E4">
-        <v>-10.9733323649843</v>
+        <v>-17.98965036604058</v>
       </c>
       <c r="F4">
-        <v>-7.513078148211815</v>
+        <v>-7.185802945227381</v>
       </c>
       <c r="G4">
-        <v>-7.496476612341413</v>
+        <v>-12.36843102357324</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>1.291963338447498</v>
       </c>
       <c r="E5">
-        <v>-10.45203707959132</v>
+        <v>-17.96946242891439</v>
       </c>
       <c r="F5">
-        <v>-7.784033601431393</v>
+        <v>-7.556596407135697</v>
       </c>
       <c r="G5">
-        <v>-7.371099631678135</v>
+        <v>-12.73467998712835</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>1.220811620344584</v>
       </c>
       <c r="E6">
-        <v>-10.713388899996</v>
+        <v>-19.73413176564539</v>
       </c>
       <c r="F6">
-        <v>-7.548049542236549</v>
+        <v>-7.891569608648604</v>
       </c>
       <c r="G6">
-        <v>-7.352686377388708</v>
+        <v>-13.88063029136538</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>1.069182922756981</v>
       </c>
       <c r="E7">
-        <v>-12.07586634620978</v>
+        <v>-20.67998054620548</v>
       </c>
       <c r="F7">
-        <v>-7.381301938252887</v>
+        <v>-7.892230014015342</v>
       </c>
       <c r="G7">
-        <v>-8.131038670763376</v>
+        <v>-13.19415722361487</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>0.8848849260042329</v>
       </c>
       <c r="E8">
-        <v>-13.34042007048168</v>
+        <v>-21.45329446707332</v>
       </c>
       <c r="F8">
-        <v>-7.139192500503603</v>
+        <v>-7.352322099632739</v>
       </c>
       <c r="G8">
-        <v>-8.106272479584087</v>
+        <v>-13.44557991514036</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>0.7121139507482507</v>
       </c>
       <c r="E9">
-        <v>-13.72702495346452</v>
+        <v>-21.43312917231717</v>
       </c>
       <c r="F9">
-        <v>-7.188147621835189</v>
+        <v>-7.510668143734995</v>
       </c>
       <c r="G9">
-        <v>-8.495327791359237</v>
+        <v>-13.20062271905307</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>0.5967036270799724</v>
       </c>
       <c r="E10">
-        <v>-14.83565878917833</v>
+        <v>-21.18604657351066</v>
       </c>
       <c r="F10">
-        <v>-7.374204956119325</v>
+        <v>-7.367504692317579</v>
       </c>
       <c r="G10">
-        <v>-8.856869159157505</v>
+        <v>-13.5229275011199</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>0.5736777286973381</v>
       </c>
       <c r="E11">
-        <v>-15.19362560253666</v>
+        <v>-21.65120236663054</v>
       </c>
       <c r="F11">
-        <v>-6.762679088755198</v>
+        <v>-7.522074389664469</v>
       </c>
       <c r="G11">
-        <v>-9.123172752882018</v>
+        <v>-13.9568390496794</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>0.6635518634631608</v>
       </c>
       <c r="E12">
-        <v>-15.48117917354972</v>
+        <v>-22.10294934821371</v>
       </c>
       <c r="F12">
-        <v>-6.616185499724091</v>
+        <v>-7.090031101476532</v>
       </c>
       <c r="G12">
-        <v>-7.964610925413134</v>
+        <v>-13.97260055699187</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>0.8691427593034226</v>
       </c>
       <c r="E13">
-        <v>-14.54058795131254</v>
+        <v>-23.43161267901221</v>
       </c>
       <c r="F13">
-        <v>-6.648848642377073</v>
+        <v>-6.958439393256753</v>
       </c>
       <c r="G13">
-        <v>-8.627991282754451</v>
+        <v>-13.71562111477872</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>1.174345138621811</v>
       </c>
       <c r="E14">
-        <v>-15.94918337682043</v>
+        <v>-23.49249801204534</v>
       </c>
       <c r="F14">
-        <v>-6.658206364704925</v>
+        <v>-7.652179789882608</v>
       </c>
       <c r="G14">
-        <v>-7.344654993910437</v>
+        <v>-12.98044826687276</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>1.546840155617242</v>
       </c>
       <c r="E15">
-        <v>-15.40161841370896</v>
+        <v>-25.54813086071718</v>
       </c>
       <c r="F15">
-        <v>-6.547397233286979</v>
+        <v>-7.412817290043654</v>
       </c>
       <c r="G15">
-        <v>-7.097264546851779</v>
+        <v>-12.4017847698814</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>1.942824187664528</v>
       </c>
       <c r="E16">
-        <v>-17.10158944229238</v>
+        <v>-23.9583511901624</v>
       </c>
       <c r="F16">
-        <v>-6.073139867996524</v>
+        <v>-6.774781373434507</v>
       </c>
       <c r="G16">
-        <v>-7.145790523366416</v>
+        <v>-12.50830488315298</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>2.313902381228459</v>
       </c>
       <c r="E17">
-        <v>-17.20894597559222</v>
+        <v>-25.73209558880478</v>
       </c>
       <c r="F17">
-        <v>-6.007489714830855</v>
+        <v>-6.874474473031984</v>
       </c>
       <c r="G17">
-        <v>-6.910417356615313</v>
+        <v>-12.19192266705592</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>2.612885222983775</v>
       </c>
       <c r="E18">
-        <v>-16.81358302387855</v>
+        <v>-25.40119093611629</v>
       </c>
       <c r="F18">
-        <v>-5.944382993365382</v>
+        <v>-6.646908602630659</v>
       </c>
       <c r="G18">
-        <v>-6.700181162143896</v>
+        <v>-12.30051187128955</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>2.798755282388261</v>
       </c>
       <c r="E19">
-        <v>-19.59266676611978</v>
+        <v>-26.30816729579454</v>
       </c>
       <c r="F19">
-        <v>-5.627728122249883</v>
+        <v>-6.504954310679681</v>
       </c>
       <c r="G19">
-        <v>-6.344350485400873</v>
+        <v>-11.98878759276624</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>2.842471565126427</v>
       </c>
       <c r="E20">
-        <v>-19.00063671672699</v>
+        <v>-27.3461659939367</v>
       </c>
       <c r="F20">
-        <v>-5.542045672959821</v>
+        <v>-6.530022791615171</v>
       </c>
       <c r="G20">
-        <v>-5.056213905524914</v>
+        <v>-11.8710513512076</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>2.725146584516412</v>
       </c>
       <c r="E21">
-        <v>-19.85873272796644</v>
+        <v>-27.09502588241932</v>
       </c>
       <c r="F21">
-        <v>-5.096544447828959</v>
+        <v>-6.164263930812037</v>
       </c>
       <c r="G21">
-        <v>-5.488485078769711</v>
+        <v>-11.44286539115826</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>2.441529938795364</v>
       </c>
       <c r="E22">
-        <v>-19.91181550028436</v>
+        <v>-26.77772476564988</v>
       </c>
       <c r="F22">
-        <v>-4.582483009912806</v>
+        <v>-5.659570905238667</v>
       </c>
       <c r="G22">
-        <v>-5.648569818866708</v>
+        <v>-10.64181268702081</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>2.000364118196829</v>
       </c>
       <c r="E23">
-        <v>-20.80651063845379</v>
+        <v>-29.34340417027964</v>
       </c>
       <c r="F23">
-        <v>-4.597529007962438</v>
+        <v>-5.556506491673699</v>
       </c>
       <c r="G23">
-        <v>-4.984990828793034</v>
+        <v>-11.04444785659805</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>1.41605369179992</v>
       </c>
       <c r="E24">
-        <v>-21.55763050821005</v>
+        <v>-29.17421132440506</v>
       </c>
       <c r="F24">
-        <v>-4.503242284433793</v>
+        <v>-5.380032557810366</v>
       </c>
       <c r="G24">
-        <v>-5.976684608354954</v>
+        <v>-11.28022822045048</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>0.7167227612392023</v>
       </c>
       <c r="E25">
-        <v>-21.40198232809241</v>
+        <v>-27.4757528061402</v>
       </c>
       <c r="F25">
-        <v>-4.113958660036242</v>
+        <v>-4.924818464300112</v>
       </c>
       <c r="G25">
-        <v>-6.104213443618758</v>
+        <v>-11.76498478267489</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-0.06220230524082728</v>
       </c>
       <c r="E26">
-        <v>-20.63238628438486</v>
+        <v>-29.12391809207587</v>
       </c>
       <c r="F26">
-        <v>-4.171302275675432</v>
+        <v>-5.7261918701305</v>
       </c>
       <c r="G26">
-        <v>-6.461606697856318</v>
+        <v>-11.73137943490574</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-0.88211719256649</v>
       </c>
       <c r="E27">
-        <v>-22.29925869644622</v>
+        <v>-27.58379766748921</v>
       </c>
       <c r="F27">
-        <v>-4.283290080220944</v>
+        <v>-5.788544747580224</v>
       </c>
       <c r="G27">
-        <v>-6.361177988376988</v>
+        <v>-12.44474571934452</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-1.696996514894507</v>
       </c>
       <c r="E28">
-        <v>-22.47260415298583</v>
+        <v>-28.34655118697116</v>
       </c>
       <c r="F28">
-        <v>-3.841908866029096</v>
+        <v>-5.376046370021204</v>
       </c>
       <c r="G28">
-        <v>-6.829176569081598</v>
+        <v>-12.14308549926059</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-2.463213743854153</v>
       </c>
       <c r="E29">
-        <v>-21.60565044658738</v>
+        <v>-30.86258040258083</v>
       </c>
       <c r="F29">
-        <v>-3.884792454807366</v>
+        <v>-5.244295499356924</v>
       </c>
       <c r="G29">
-        <v>-6.798365321747601</v>
+        <v>-12.05922275965977</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-3.137876376052916</v>
       </c>
       <c r="E30">
-        <v>-21.97166435825734</v>
+        <v>-28.44223331427923</v>
       </c>
       <c r="F30">
-        <v>-3.993034003009905</v>
+        <v>-5.027921678660009</v>
       </c>
       <c r="G30">
-        <v>-7.520448272591276</v>
+        <v>-12.81053782761521</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-3.680825989902244</v>
       </c>
       <c r="E31">
-        <v>-21.05948931041829</v>
+        <v>-29.0119379868142</v>
       </c>
       <c r="F31">
-        <v>-3.92075683244108</v>
+        <v>-4.629745545547266</v>
       </c>
       <c r="G31">
-        <v>-6.719143966992842</v>
+        <v>-13.95138492590345</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-4.060616902711184</v>
       </c>
       <c r="E32">
-        <v>-20.77087154801343</v>
+        <v>-28.65387607550171</v>
       </c>
       <c r="F32">
-        <v>-3.695456453351791</v>
+        <v>-5.082919033985474</v>
       </c>
       <c r="G32">
-        <v>-7.60569150968197</v>
+        <v>-11.56122070473274</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-4.251166173863296</v>
       </c>
       <c r="E33">
-        <v>-21.11237735835387</v>
+        <v>-30.42637514379198</v>
       </c>
       <c r="F33">
-        <v>-4.113291919845842</v>
+        <v>-5.621451895706997</v>
       </c>
       <c r="G33">
-        <v>-6.873435252396115</v>
+        <v>-11.74579686072927</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-4.23867716866466</v>
       </c>
       <c r="E34">
-        <v>-21.00916890724506</v>
+        <v>-28.10630658391624</v>
       </c>
       <c r="F34">
-        <v>-3.745880857846426</v>
+        <v>-4.694978392204217</v>
       </c>
       <c r="G34">
-        <v>-7.182534268306787</v>
+        <v>-12.70012451278944</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-4.018871172528812</v>
       </c>
       <c r="E35">
-        <v>-20.20458134488024</v>
+        <v>-28.09895234212778</v>
       </c>
       <c r="F35">
-        <v>-3.688341654526679</v>
+        <v>-5.168539718744835</v>
       </c>
       <c r="G35">
-        <v>-7.362101568902395</v>
+        <v>-13.17737606827631</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-3.59994374462803</v>
       </c>
       <c r="E36">
-        <v>-19.04329041340524</v>
+        <v>-28.82968955037551</v>
       </c>
       <c r="F36">
-        <v>-3.800116450626565</v>
+        <v>-4.954808311367832</v>
       </c>
       <c r="G36">
-        <v>-7.037595274051955</v>
+        <v>-11.12789677800646</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-3.002662990878957</v>
       </c>
       <c r="E37">
-        <v>-20.14677990264634</v>
+        <v>-28.00959649300843</v>
       </c>
       <c r="F37">
-        <v>-4.381030866351162</v>
+        <v>-5.05814353864434</v>
       </c>
       <c r="G37">
-        <v>-7.642378975348173</v>
+        <v>-12.42401839372314</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-2.2563325767783</v>
       </c>
       <c r="E38">
-        <v>-19.00389721801252</v>
+        <v>-27.3195385667716</v>
       </c>
       <c r="F38">
-        <v>-3.863627808953433</v>
+        <v>-4.692548195476975</v>
       </c>
       <c r="G38">
-        <v>-6.822949432922229</v>
+        <v>-11.88371749844085</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-1.40326540086847</v>
       </c>
       <c r="E39">
-        <v>-19.39056097115745</v>
+        <v>-26.28208328551035</v>
       </c>
       <c r="F39">
-        <v>-3.94030768196718</v>
+        <v>-5.289983831311436</v>
       </c>
       <c r="G39">
-        <v>-6.726420546088161</v>
+        <v>-12.12211650381484</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-0.4858626633492651</v>
       </c>
       <c r="E40">
-        <v>-17.83135755710246</v>
+        <v>-26.4911674589185</v>
       </c>
       <c r="F40">
-        <v>-3.864372150733689</v>
+        <v>-4.844456475032969</v>
       </c>
       <c r="G40">
-        <v>-6.884416331949877</v>
+        <v>-11.49146088912922</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>0.4530503670188389</v>
       </c>
       <c r="E41">
-        <v>-18.73244690057073</v>
+        <v>-25.2588519411072</v>
       </c>
       <c r="F41">
-        <v>-4.271385362854585</v>
+        <v>-4.657515828774496</v>
       </c>
       <c r="G41">
-        <v>-6.374307611985738</v>
+        <v>-11.65743508974058</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>1.37022228324645</v>
       </c>
       <c r="E42">
-        <v>-18.4405414660363</v>
+        <v>-26.49546498075178</v>
       </c>
       <c r="F42">
-        <v>-4.065171015605214</v>
+        <v>-5.245823775565323</v>
       </c>
       <c r="G42">
-        <v>-6.47586190694842</v>
+        <v>-11.73173035273291</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>2.238988521730275</v>
       </c>
       <c r="E43">
-        <v>-17.07118979627889</v>
+        <v>-26.88622247439965</v>
       </c>
       <c r="F43">
-        <v>-3.760415318885371</v>
+        <v>-4.826202680651614</v>
       </c>
       <c r="G43">
-        <v>-5.665304626567724</v>
+        <v>-10.60346663803943</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>3.034482097813002</v>
       </c>
       <c r="E44">
-        <v>-16.59905109623918</v>
+        <v>-26.03890423129846</v>
       </c>
       <c r="F44">
-        <v>-4.340635279566048</v>
+        <v>-4.572089939842734</v>
       </c>
       <c r="G44">
-        <v>-6.406764200452752</v>
+        <v>-12.31071166209605</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>3.742515416522401</v>
       </c>
       <c r="E45">
-        <v>-18.56415069254967</v>
+        <v>-25.22390570719001</v>
       </c>
       <c r="F45">
-        <v>-4.081868818924651</v>
+        <v>-5.334249203500926</v>
       </c>
       <c r="G45">
-        <v>-6.613673296657201</v>
+        <v>-10.99518362842816</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>4.363780697004694</v>
       </c>
       <c r="E46">
-        <v>-16.00858789885304</v>
+        <v>-25.29674168312938</v>
       </c>
       <c r="F46">
-        <v>-3.849627848660948</v>
+        <v>-4.976624652205968</v>
       </c>
       <c r="G46">
-        <v>-5.907994098960616</v>
+        <v>-10.73442188793638</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>4.896424879685259</v>
       </c>
       <c r="E47">
-        <v>-16.65556192338089</v>
+        <v>-26.3448705776267</v>
       </c>
       <c r="F47">
-        <v>-4.229436952419383</v>
+        <v>-4.725383962074738</v>
       </c>
       <c r="G47">
-        <v>-5.822188069128246</v>
+        <v>-11.44170670021951</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>5.347629445218803</v>
       </c>
       <c r="E48">
-        <v>-15.63138412791013</v>
+        <v>-25.01194142431298</v>
       </c>
       <c r="F48">
-        <v>-4.097823072316787</v>
+        <v>-5.2968167304836</v>
       </c>
       <c r="G48">
-        <v>-5.315307131064895</v>
+        <v>-13.22043302356007</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>5.726308405487814</v>
       </c>
       <c r="E49">
-        <v>-16.83311886074764</v>
+        <v>-24.59330211619989</v>
       </c>
       <c r="F49">
-        <v>-4.345338886134903</v>
+        <v>-5.090254759785791</v>
       </c>
       <c r="G49">
-        <v>-5.98356061144002</v>
+        <v>-10.55073626868992</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>6.035791818244574</v>
       </c>
       <c r="E50">
-        <v>-15.07224891370907</v>
+        <v>-23.89698131041045</v>
       </c>
       <c r="F50">
-        <v>-4.626641481953004</v>
+        <v>-5.592078110240384</v>
       </c>
       <c r="G50">
-        <v>-5.286869544882555</v>
+        <v>-11.82293257179429</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>6.282166280779138</v>
       </c>
       <c r="E51">
-        <v>-14.48568926091755</v>
+        <v>-22.96604479475763</v>
       </c>
       <c r="F51">
-        <v>-4.669685816881691</v>
+        <v>-5.350943047555574</v>
       </c>
       <c r="G51">
-        <v>-5.634453652687255</v>
+        <v>-10.71124806916148</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>6.465950009205731</v>
       </c>
       <c r="E52">
-        <v>-14.82494441967618</v>
+        <v>-21.96909218502098</v>
       </c>
       <c r="F52">
-        <v>-4.561584426652667</v>
+        <v>-5.180182332782189</v>
       </c>
       <c r="G52">
-        <v>-5.159065934338991</v>
+        <v>-10.95263649715744</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>6.584389253403423</v>
       </c>
       <c r="E53">
-        <v>-13.86266633541627</v>
+        <v>-23.5513953449891</v>
       </c>
       <c r="F53">
-        <v>-4.494965045466749</v>
+        <v>-5.814870691012574</v>
       </c>
       <c r="G53">
-        <v>-4.806420002404746</v>
+        <v>-10.84204441287255</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>6.636635384111551</v>
       </c>
       <c r="E54">
-        <v>-14.57121854950042</v>
+        <v>-22.83344654733903</v>
       </c>
       <c r="F54">
-        <v>-4.831951533124659</v>
+        <v>-5.245500699558573</v>
       </c>
       <c r="G54">
-        <v>-5.536123829079822</v>
+        <v>-10.82305843420483</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>6.619972151385507</v>
       </c>
       <c r="E55">
-        <v>-14.13518537272386</v>
+        <v>-21.92103149037758</v>
       </c>
       <c r="F55">
-        <v>-4.810447974204822</v>
+        <v>-5.567720713260925</v>
       </c>
       <c r="G55">
-        <v>-6.014798919148583</v>
+        <v>-11.31819686724038</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>6.531329859444803</v>
       </c>
       <c r="E56">
-        <v>-12.19631016939178</v>
+        <v>-22.63282609185122</v>
       </c>
       <c r="F56">
-        <v>-4.77702465271243</v>
+        <v>-5.28314142990378</v>
       </c>
       <c r="G56">
-        <v>-5.46150413262465</v>
+        <v>-11.08902435228434</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>6.368758989522328</v>
       </c>
       <c r="E57">
-        <v>-13.44921665851597</v>
+        <v>-21.15854062238807</v>
       </c>
       <c r="F57">
-        <v>-4.427997248979434</v>
+        <v>-5.938226336619111</v>
       </c>
       <c r="G57">
-        <v>-6.012799349642863</v>
+        <v>-11.42088998986858</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>6.133362934807344</v>
       </c>
       <c r="E58">
-        <v>-12.71717977822804</v>
+        <v>-21.55171632115603</v>
       </c>
       <c r="F58">
-        <v>-4.991616012401518</v>
+        <v>-5.159657504118093</v>
       </c>
       <c r="G58">
-        <v>-5.41199492408485</v>
+        <v>-11.32979701880999</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>5.827622990112038</v>
       </c>
       <c r="E59">
-        <v>-13.35875133326473</v>
+        <v>-22.21185009115017</v>
       </c>
       <c r="F59">
-        <v>-5.007492664203798</v>
+        <v>-5.837383070600547</v>
       </c>
       <c r="G59">
-        <v>-5.310126127295936</v>
+        <v>-12.50234259063676</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>5.458459097764341</v>
       </c>
       <c r="E60">
-        <v>-13.16566625852569</v>
+        <v>-21.08171958932195</v>
       </c>
       <c r="F60">
-        <v>-4.626479152096672</v>
+        <v>-5.5041111651673</v>
       </c>
       <c r="G60">
-        <v>-6.111350979801427</v>
+        <v>-12.59657726941211</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>5.037391365136594</v>
       </c>
       <c r="E61">
-        <v>-13.0333714188656</v>
+        <v>-20.63567848498844</v>
       </c>
       <c r="F61">
-        <v>-5.058617858566015</v>
+        <v>-5.956005019225834</v>
       </c>
       <c r="G61">
-        <v>-6.489196784380605</v>
+        <v>-11.52130545716575</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>4.575282064646846</v>
       </c>
       <c r="E62">
-        <v>-11.38310039251636</v>
+        <v>-19.93270987935574</v>
       </c>
       <c r="F62">
-        <v>-4.722279898480477</v>
+        <v>-6.447179927031492</v>
       </c>
       <c r="G62">
-        <v>-5.753020841176253</v>
+        <v>-12.15364282898532</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>4.089748971194224</v>
       </c>
       <c r="E63">
-        <v>-11.96577008613529</v>
+        <v>-19.37664044205787</v>
       </c>
       <c r="F63">
-        <v>-5.000943248390498</v>
+        <v>-5.571650679490088</v>
       </c>
       <c r="G63">
-        <v>-6.622436310699652</v>
+        <v>-12.35118970240471</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>3.599239363869867</v>
       </c>
       <c r="E64">
-        <v>-11.6049910904182</v>
+        <v>-21.75613616633628</v>
       </c>
       <c r="F64">
-        <v>-4.866396344932509</v>
+        <v>-5.838064855997143</v>
       </c>
       <c r="G64">
-        <v>-5.956566423112803</v>
+        <v>-12.05288306495206</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>3.120570975826047</v>
       </c>
       <c r="E65">
-        <v>-11.56052147566288</v>
+        <v>-21.56797807131757</v>
       </c>
       <c r="F65">
-        <v>-4.461608239622806</v>
+        <v>-5.827721672663408</v>
       </c>
       <c r="G65">
-        <v>-5.99609764739724</v>
+        <v>-12.96126365547269</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>2.674834019252014</v>
       </c>
       <c r="E66">
-        <v>-11.37761188201907</v>
+        <v>-20.922937705191</v>
       </c>
       <c r="F66">
-        <v>-5.310251307764273</v>
+        <v>-5.413567530569796</v>
       </c>
       <c r="G66">
-        <v>-6.879844468560144</v>
+        <v>-12.68502511458482</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>2.277425292758013</v>
       </c>
       <c r="E67">
-        <v>-11.18525136312125</v>
+        <v>-21.56392508708071</v>
       </c>
       <c r="F67">
-        <v>-5.029984455614869</v>
+        <v>-5.857249869456776</v>
       </c>
       <c r="G67">
-        <v>-6.325324780186681</v>
+        <v>-12.19912641414937</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>1.941548239909492</v>
       </c>
       <c r="E68">
-        <v>-12.82104032959396</v>
+        <v>-19.73004255361647</v>
       </c>
       <c r="F68">
-        <v>-4.945408224906741</v>
+        <v>-5.534882571104288</v>
       </c>
       <c r="G68">
-        <v>-7.77975668359131</v>
+        <v>-11.4786788728021</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>1.680639442494458</v>
       </c>
       <c r="E69">
-        <v>-11.74387938823345</v>
+        <v>-21.24951766520216</v>
       </c>
       <c r="F69">
-        <v>-5.049390396049707</v>
+        <v>-5.88311257890886</v>
       </c>
       <c r="G69">
-        <v>-6.771837920341421</v>
+        <v>-12.88951420200006</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>1.502242263826552</v>
       </c>
       <c r="E70">
-        <v>-11.72893089553413</v>
+        <v>-21.07971347533655</v>
       </c>
       <c r="F70">
-        <v>-4.529284744507279</v>
+        <v>-5.671106619126728</v>
       </c>
       <c r="G70">
-        <v>-6.640021928604261</v>
+        <v>-12.44458350261309</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>1.412225118278157</v>
       </c>
       <c r="E71">
-        <v>-12.12980500011514</v>
+        <v>-20.68196854629485</v>
       </c>
       <c r="F71">
-        <v>-5.069162964403968</v>
+        <v>-6.212538850452941</v>
       </c>
       <c r="G71">
-        <v>-6.544055834511868</v>
+        <v>-12.5491834994719</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>1.411266514687872</v>
       </c>
       <c r="E72">
-        <v>-11.492693991976</v>
+        <v>-21.25807648107666</v>
       </c>
       <c r="F72">
-        <v>-4.941562195091096</v>
+        <v>-5.834839638900351</v>
       </c>
       <c r="G72">
-        <v>-6.799835203967038</v>
+        <v>-12.75984344377235</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>1.493967795869851</v>
       </c>
       <c r="E73">
-        <v>-12.06685921140852</v>
+        <v>-21.59538439601199</v>
       </c>
       <c r="F73">
-        <v>-4.913332637148388</v>
+        <v>-5.911475168148465</v>
       </c>
       <c r="G73">
-        <v>-6.566269595080377</v>
+        <v>-12.86809497236098</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>1.651412555551256</v>
       </c>
       <c r="E74">
-        <v>-12.39210780006143</v>
+        <v>-22.1212443832047</v>
       </c>
       <c r="F74">
-        <v>-5.445773774066172</v>
+        <v>-5.879062251030124</v>
       </c>
       <c r="G74">
-        <v>-6.580365897986594</v>
+        <v>-11.33146553376178</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>1.866304130483266</v>
       </c>
       <c r="E75">
-        <v>-12.59593894362068</v>
+        <v>-22.19471887397915</v>
       </c>
       <c r="F75">
-        <v>-5.266773829267714</v>
+        <v>-6.24199063343589</v>
       </c>
       <c r="G75">
-        <v>-6.94749877720069</v>
+        <v>-12.69679079343139</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>2.11963811099181</v>
       </c>
       <c r="E76">
-        <v>-13.63729776947654</v>
+        <v>-22.20571853734378</v>
       </c>
       <c r="F76">
-        <v>-5.516950269023767</v>
+        <v>-6.439558738239918</v>
       </c>
       <c r="G76">
-        <v>-7.050933462029679</v>
+        <v>-13.68714214677713</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>2.390329237694611</v>
       </c>
       <c r="E77">
-        <v>-13.63513768737488</v>
+        <v>-23.13044198665808</v>
       </c>
       <c r="F77">
-        <v>-5.410459507710746</v>
+        <v>-6.118053767758387</v>
       </c>
       <c r="G77">
-        <v>-6.681377263480837</v>
+        <v>-13.13869565419546</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>2.656819031056695</v>
       </c>
       <c r="E78">
-        <v>-14.13545708116432</v>
+        <v>-22.23816958208275</v>
       </c>
       <c r="F78">
-        <v>-5.196748688510643</v>
+        <v>-6.014465939388366</v>
       </c>
       <c r="G78">
-        <v>-6.234211945854859</v>
+        <v>-13.54584971843381</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>2.901608687430231</v>
       </c>
       <c r="E79">
-        <v>-14.78749393963275</v>
+        <v>-22.65103508583606</v>
       </c>
       <c r="F79">
-        <v>-5.723039503505818</v>
+        <v>-5.90970616864092</v>
       </c>
       <c r="G79">
-        <v>-6.427365725343637</v>
+        <v>-12.62810690512813</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>3.11080455793375</v>
       </c>
       <c r="E80">
-        <v>-15.21156288808104</v>
+        <v>-23.64444642889871</v>
       </c>
       <c r="F80">
-        <v>-5.338075436992629</v>
+        <v>-6.034448348776423</v>
       </c>
       <c r="G80">
-        <v>-7.221926449678575</v>
+        <v>-11.37169197260947</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>3.276878313550561</v>
       </c>
       <c r="E81">
-        <v>-15.77271780168953</v>
+        <v>-24.60218698220294</v>
       </c>
       <c r="F81">
-        <v>-5.624661275744635</v>
+        <v>-6.726706396665428</v>
       </c>
       <c r="G81">
-        <v>-7.028607142912834</v>
+        <v>-12.41168661158935</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>3.397266361438255</v>
       </c>
       <c r="E82">
-        <v>-16.29087938306919</v>
+        <v>-25.22351625842535</v>
       </c>
       <c r="F82">
-        <v>-5.564580224430609</v>
+        <v>-6.227826363654678</v>
       </c>
       <c r="G82">
-        <v>-6.093689219349415</v>
+        <v>-11.89670476859141</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>3.471899868238304</v>
       </c>
       <c r="E83">
-        <v>-17.08304986970498</v>
+        <v>-25.62448998943452</v>
       </c>
       <c r="F83">
-        <v>-5.280972544652585</v>
+        <v>-6.482095891349186</v>
       </c>
       <c r="G83">
-        <v>-6.564723570313538</v>
+        <v>-11.39354819425974</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>3.504796244388507</v>
       </c>
       <c r="E84">
-        <v>-18.14508570787986</v>
+        <v>-25.83928004009233</v>
       </c>
       <c r="F84">
-        <v>-5.625278129198699</v>
+        <v>-6.429641175870958</v>
       </c>
       <c r="G84">
-        <v>-7.092378181635815</v>
+        <v>-12.63079506810602</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>3.501482919088456</v>
       </c>
       <c r="E85">
-        <v>-18.85511420449051</v>
+        <v>-26.67208452399894</v>
       </c>
       <c r="F85">
-        <v>-5.718348566584287</v>
+        <v>-6.285475238609068</v>
       </c>
       <c r="G85">
-        <v>-6.355467297321745</v>
+        <v>-13.33600747888157</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>3.466608199088856</v>
       </c>
       <c r="E86">
-        <v>-20.54999975676332</v>
+        <v>-29.73777765042263</v>
       </c>
       <c r="F86">
-        <v>-5.856565708501306</v>
+        <v>-6.122457657982745</v>
       </c>
       <c r="G86">
-        <v>-6.527688497365711</v>
+        <v>-12.28242636100851</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>3.401647408188413</v>
       </c>
       <c r="E87">
-        <v>-21.47621760250015</v>
+        <v>-28.83409122711096</v>
       </c>
       <c r="F87">
-        <v>-5.658174868474207</v>
+        <v>-6.81250326870788</v>
       </c>
       <c r="G87">
-        <v>-5.452400132391654</v>
+        <v>-11.64341492938177</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>3.30540920854097</v>
       </c>
       <c r="E88">
-        <v>-22.45260188329395</v>
+        <v>-29.66973959269439</v>
       </c>
       <c r="F88">
-        <v>-5.522511452345833</v>
+        <v>-6.667493612119541</v>
       </c>
       <c r="G88">
-        <v>-5.473210221651513</v>
+        <v>-11.73701067286804</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>3.173057290932119</v>
       </c>
       <c r="E89">
-        <v>-23.12565538963198</v>
+        <v>-29.96286545097389</v>
       </c>
       <c r="F89">
-        <v>-6.042313824205453</v>
+        <v>-6.572582908460213</v>
       </c>
       <c r="G89">
-        <v>-7.4408462050995</v>
+        <v>-11.69800251477881</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>2.998347865866521</v>
       </c>
       <c r="E90">
-        <v>-25.01468567956163</v>
+        <v>-30.53481624661666</v>
       </c>
       <c r="F90">
-        <v>-6.080245164586144</v>
+        <v>-6.776555519986278</v>
       </c>
       <c r="G90">
-        <v>-6.656746804668659</v>
+        <v>-12.02934508616785</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>2.77700946800695</v>
       </c>
       <c r="E91">
-        <v>-26.32389015754917</v>
+        <v>-34.14701920170803</v>
       </c>
       <c r="F91">
-        <v>-5.929051136398012</v>
+        <v>-6.284843339948808</v>
       </c>
       <c r="G91">
-        <v>-6.79505808675387</v>
+        <v>-12.01182898971956</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>2.502343627772843</v>
       </c>
       <c r="E92">
-        <v>-28.13765720947134</v>
+        <v>-35.18841425535595</v>
       </c>
       <c r="F92">
-        <v>-5.694587434881991</v>
+        <v>-6.263863987686982</v>
       </c>
       <c r="G92">
-        <v>-6.636777593975775</v>
+        <v>-12.4749743106636</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>2.172598873299738</v>
       </c>
       <c r="E93">
-        <v>-30.57857262671578</v>
+        <v>-34.40643962794844</v>
       </c>
       <c r="F93">
-        <v>-5.999879216054211</v>
+        <v>-5.913712944606981</v>
       </c>
       <c r="G93">
-        <v>-6.738444447486793</v>
+        <v>-13.78292947141041</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>1.790222241860107</v>
       </c>
       <c r="E94">
-        <v>-32.48021245251979</v>
+        <v>-37.63620842461804</v>
       </c>
       <c r="F94">
-        <v>-5.860402236081459</v>
+        <v>-6.79340060795585</v>
       </c>
       <c r="G94">
-        <v>-6.984404738872485</v>
+        <v>-11.99570663294331</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>1.357365410725379</v>
       </c>
       <c r="E95">
-        <v>-33.85480130246707</v>
+        <v>-38.17893697748932</v>
       </c>
       <c r="F95">
-        <v>-6.196796417726994</v>
+        <v>-6.330515438917687</v>
       </c>
       <c r="G95">
-        <v>-7.679834487579488</v>
+        <v>-12.88811715178249</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>0.8785882709828982</v>
       </c>
       <c r="E96">
-        <v>-36.34481669913968</v>
+        <v>-40.68831839325573</v>
       </c>
       <c r="F96">
-        <v>-5.689553625629767</v>
+        <v>-6.156347380867234</v>
       </c>
       <c r="G96">
-        <v>-8.052810479670397</v>
+        <v>-12.57575724851564</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>0.3681551410467082</v>
       </c>
       <c r="E97">
-        <v>-38.01088077859067</v>
+        <v>-43.4505426267664</v>
       </c>
       <c r="F97">
-        <v>-5.781033230423295</v>
+        <v>-6.188013976572925</v>
       </c>
       <c r="G97">
-        <v>-7.782643479301554</v>
+        <v>-13.10818897705108</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-0.1789825002766443</v>
       </c>
       <c r="E98">
-        <v>-40.31843490054622</v>
+        <v>-43.89925100229042</v>
       </c>
       <c r="F98">
-        <v>-5.953476632731835</v>
+        <v>-6.094085170581168</v>
       </c>
       <c r="G98">
-        <v>-8.779399082993018</v>
+        <v>-13.26887292589069</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-0.7337964619912972</v>
       </c>
       <c r="E99">
-        <v>-43.43466806113251</v>
+        <v>-45.9275114898229</v>
       </c>
       <c r="F99">
-        <v>-5.726940963028503</v>
+        <v>-5.641247427797032</v>
       </c>
       <c r="G99">
-        <v>-7.821098776285728</v>
+        <v>-13.91126773505856</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-1.316799506236108</v>
       </c>
       <c r="E100">
-        <v>-44.69432197652812</v>
+        <v>-48.19313647094143</v>
       </c>
       <c r="F100">
-        <v>-5.952660232332426</v>
+        <v>-6.106734625654262</v>
       </c>
       <c r="G100">
-        <v>-9.263937149211829</v>
+        <v>-14.03861449031771</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-1.871650850725617</v>
       </c>
       <c r="E101">
-        <v>-47.12086628150922</v>
+        <v>-51.22834051398998</v>
       </c>
       <c r="F101">
-        <v>-6.079861115901649</v>
+        <v>-5.886674333512683</v>
       </c>
       <c r="G101">
-        <v>-9.610057995888171</v>
+        <v>-14.0625298712934</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-2.460529514757171</v>
       </c>
       <c r="E102">
-        <v>-50.0046551355188</v>
+        <v>-52.90086219737591</v>
       </c>
       <c r="F102">
-        <v>-5.727360645096095</v>
+        <v>-5.762687581098845</v>
       </c>
       <c r="G102">
-        <v>-8.895533020510653</v>
+        <v>-14.45353012857288</v>
       </c>
     </row>
   </sheetData>
